--- a/data/trans_orig/IP31KM11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM11_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58635</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55988</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59811</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>70732</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68020</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>54288</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>52079</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>72645</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>69069</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>74047</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>143377</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139475</t>
+          <t>109336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145318</t>
+          <t>114546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1628</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2843</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5538</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>113049</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>108939</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>99333</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>124478</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>119876</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>126423</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>291</t>
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>250126</t>
+          <t>212382</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>245637</t>
+          <t>207553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6547</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6731</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56321</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53016</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53716</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>50358</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55052</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>51992</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>48029</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53464</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>108313</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>104262</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>110414</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>63502</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>60796</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>64633</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>117218</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>113611</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>119423</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4283</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5194</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6083</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7149</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1131</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3837</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2967</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6574</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61049</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>67728</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63467</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>69200</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>68561</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67826</t>
+          <t>64232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>140976</t>
+          <t>135654</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134847</t>
+          <t>129249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143574</t>
+          <t>138795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8767</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6215</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>138</t>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>45768</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>43249</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46821</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>91,61%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>42599</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>39782</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>43773</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>43719</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95001</t>
+          <t>88222</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91503</t>
+          <t>84643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96830</t>
+          <t>90264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,74 +2778,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>137126</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>132925</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>139440</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>121822</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>146890</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>153300</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>345</t>
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>270586</t>
+          <t>258949</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246041</t>
+          <t>254268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>277288</t>
+          <t>261159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7646</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>8154</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>30796</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,74 +3121,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>152516</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>146660</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>155721</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>127941</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>124796</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>137256</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>134592</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>137900</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>148963</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>141616</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>152663</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>380</t>
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>276902</t>
+          <t>289772</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>268854</t>
+          <t>283298</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280307</t>
+          <t>292893</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10476</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3869</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>12543</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>670086</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>662166</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>676812</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>646262</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>640876</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>649796</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>611077</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>699061</t>
+          <t>605353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>731853</t>
+          <t>614642</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1369107</t>
+          <t>1281162</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1347114</t>
+          <t>1271295</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1379103</t>
+          <t>1288578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>24658</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>6872</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>12258</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50753</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
